--- a/dataset/review result/go_result_gpt-4-turbo-preview_2024-04-07 15_06_53.xlsx
+++ b/dataset/review result/go_result_gpt-4-turbo-preview_2024-04-07 15_06_53.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\oywy2\Desktop\dataset\review result\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\LLM-CMT\dataset\review result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45DA4EFC-D55E-49D8-AE51-5261ED0C885F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FC6B6C-94CF-4C60-94F1-0FA1DB63626B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-690" windowWidth="38640" windowHeight="21120" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27830" yWindow="-1880" windowWidth="20240" windowHeight="13260" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="2" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="176">
   <si>
     <t>absolute_path</t>
   </si>
@@ -548,6 +548,14 @@
   </si>
   <si>
     <t>Use of cryptographically insecure random number generator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>289ms17010.go</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>D:\Users\oywy2\PycharmProjects\chatgptCMT\dataset\Go_code\23_1_12_go\data1\1\289ms17010.go</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -558,7 +566,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/m/d\ h:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -575,12 +583,18 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -602,7 +616,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -610,6 +624,8 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -855,7 +871,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47C696A7-842D-4B76-B52E-625C1E2EBDA6}" name="数据透视表1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{47C696A7-842D-4B76-B52E-625C1E2EBDA6}" name="数据透视表1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="值" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:A42" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
     <pivotField axis="axisRow" showAll="0">
@@ -1337,207 +1353,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EFC61E7-D7A4-46E4-BE1A-2E66E1C455A2}">
   <dimension ref="A3:A42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="24.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1">
       <c r="A4" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1">
       <c r="A5" s="3" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1">
       <c r="A6" s="3" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1">
       <c r="A7" s="3" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1">
       <c r="A9" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1">
       <c r="A10" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1">
       <c r="A11" s="3" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1">
       <c r="A12" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1">
       <c r="A13" s="3" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1">
       <c r="A14" s="3" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1">
       <c r="A15" s="3" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1">
       <c r="A17" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1">
       <c r="A18" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1">
       <c r="A19" s="3" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1">
       <c r="A20" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1">
       <c r="A21" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1">
       <c r="A22" s="3" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1">
       <c r="A23" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1">
       <c r="A24" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1">
       <c r="A25" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1">
       <c r="A26" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1">
       <c r="A27" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1">
       <c r="A28" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1">
       <c r="A29" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1">
       <c r="A30" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1">
       <c r="A31" s="3" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1">
       <c r="A32" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1">
       <c r="A33" s="3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1">
       <c r="A34" s="3" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1">
       <c r="A35" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1">
       <c r="A36" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1">
       <c r="A37" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1">
       <c r="A38" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1">
       <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1">
       <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1">
       <c r="A41" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1">
       <c r="A42" s="3" t="s">
         <v>170</v>
       </c>
@@ -1551,13 +1567,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M55"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="6" max="6" width="61.1796875" customWidth="1"/>
     <col min="7" max="7" width="26.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1598,7 +1614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1636,7 +1652,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -1674,7 +1690,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>20</v>
       </c>
@@ -1709,7 +1725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1744,7 +1760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1782,7 +1798,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>30</v>
       </c>
@@ -1820,12 +1836,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
+    <row r="8" spans="1:13">
+      <c r="A8" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>174</v>
       </c>
       <c r="C8">
         <v>-1</v>
@@ -1836,7 +1852,7 @@
       <c r="E8">
         <v>2349</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="6" t="s">
         <v>172</v>
       </c>
       <c r="G8" t="s">
@@ -1854,11 +1870,11 @@
       <c r="K8">
         <v>1</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>34</v>
       </c>
@@ -1893,7 +1909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -1909,7 +1925,7 @@
       <c r="E10">
         <v>2351</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="6" t="s">
         <v>173</v>
       </c>
       <c r="G10" t="s">
@@ -1927,11 +1943,11 @@
       <c r="K10">
         <v>1</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -1966,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -2004,7 +2020,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>50</v>
       </c>
@@ -2039,7 +2055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -2074,7 +2090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -2109,7 +2125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -2144,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>60</v>
       </c>
@@ -2179,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>62</v>
       </c>
@@ -2214,7 +2230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -2249,7 +2265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -2284,7 +2300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>68</v>
       </c>
@@ -2319,7 +2335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>70</v>
       </c>
@@ -2357,7 +2373,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>74</v>
       </c>
@@ -2395,7 +2411,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>74</v>
       </c>
@@ -2430,7 +2446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>80</v>
       </c>
@@ -2468,7 +2484,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
         <v>84</v>
       </c>
@@ -2506,7 +2522,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
         <v>86</v>
       </c>
@@ -2541,7 +2557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>90</v>
       </c>
@@ -2576,7 +2592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>92</v>
       </c>
@@ -2614,7 +2630,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
         <v>96</v>
       </c>
@@ -2649,7 +2665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
         <v>96</v>
       </c>
@@ -2684,7 +2700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
         <v>96</v>
       </c>
@@ -2719,7 +2735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
         <v>104</v>
       </c>
@@ -2757,7 +2773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
         <v>104</v>
       </c>
@@ -2792,7 +2808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -2830,7 +2846,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
         <v>112</v>
       </c>
@@ -2865,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
         <v>112</v>
       </c>
@@ -2900,7 +2916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
         <v>30</v>
       </c>
@@ -2935,7 +2951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
         <v>30</v>
       </c>
@@ -2970,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
         <v>122</v>
       </c>
@@ -3008,7 +3024,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
         <v>126</v>
       </c>
@@ -3046,7 +3062,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13">
       <c r="A42" t="s">
         <v>26</v>
       </c>
@@ -3084,7 +3100,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13">
       <c r="A43" t="s">
         <v>132</v>
       </c>
@@ -3119,7 +3135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13">
       <c r="A44" t="s">
         <v>134</v>
       </c>
@@ -3154,7 +3170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13">
       <c r="A45" t="s">
         <v>138</v>
       </c>
@@ -3189,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13">
       <c r="A46" t="s">
         <v>140</v>
       </c>
@@ -3224,7 +3240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13">
       <c r="A47" t="s">
         <v>144</v>
       </c>
@@ -3262,7 +3278,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13">
       <c r="A48" t="s">
         <v>148</v>
       </c>
@@ -3297,7 +3313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13">
       <c r="A49" t="s">
         <v>152</v>
       </c>
@@ -3335,7 +3351,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13">
       <c r="A50" t="s">
         <v>152</v>
       </c>
@@ -3370,7 +3386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13">
       <c r="A51" t="s">
         <v>158</v>
       </c>
@@ -3405,7 +3421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13">
       <c r="A52" t="s">
         <v>152</v>
       </c>
@@ -3443,7 +3459,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13">
       <c r="A53" t="s">
         <v>152</v>
       </c>
@@ -3478,7 +3494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13">
       <c r="A54" t="s">
         <v>92</v>
       </c>
@@ -3516,7 +3532,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13">
       <c r="A55" t="s">
         <v>41</v>
       </c>
